--- a/INTC.xlsx
+++ b/INTC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B685DC0-B2C7-423D-B2A2-0D68F067C56B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{328D754F-49C1-46E5-A722-8BCCC53F0D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5150" yWindow="2160" windowWidth="23710" windowHeight="16930" activeTab="1" xr2:uid="{2060C4C8-3805-4E23-AE6B-F728D7027876}"/>
+    <workbookView xWindow="6080" yWindow="2630" windowWidth="23870" windowHeight="16560" activeTab="1" xr2:uid="{2060C4C8-3805-4E23-AE6B-F728D7027876}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -163,7 +163,7 @@
     39% GM non-gaap given Q422</t>
       </text>
     </comment>
-    <comment ref="U103" authorId="13" shapeId="0" xr:uid="{0577A713-2E0A-4E75-AF08-F9FA53908FBE}">
+    <comment ref="U104" authorId="13" shapeId="0" xr:uid="{0577A713-2E0A-4E75-AF08-F9FA53908FBE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -171,7 +171,7 @@
     Intel 7 node impairment</t>
       </text>
     </comment>
-    <comment ref="Y103" authorId="14" shapeId="0" xr:uid="{5269F9CD-AF19-4286-A693-FA2526B14A05}">
+    <comment ref="Y104" authorId="14" shapeId="0" xr:uid="{5269F9CD-AF19-4286-A693-FA2526B14A05}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="300">
   <si>
     <t>Price</t>
   </si>
@@ -1093,7 +1093,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -1128,12 +1128,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2703,7 +2697,7 @@
     <xdr:to>
       <xdr:col>90</xdr:col>
       <xdr:colOff>36034</xdr:colOff>
-      <xdr:row>114</xdr:row>
+      <xdr:row>115</xdr:row>
       <xdr:rowOff>54841</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2745,16 +2739,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>44274</xdr:colOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>22187</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>44274</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>107156</xdr:rowOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>22187</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>132521</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2769,8 +2763,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17272618" y="0"/>
-          <a:ext cx="0" cy="17260094"/>
+          <a:off x="17796665" y="0"/>
+          <a:ext cx="0" cy="19464130"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -3174,10 +3168,10 @@
   <threadedComment ref="O32" dT="2023-02-01T15:28:03.45" personId="{885FAFCD-EA21-4344-9B78-0E93CEEF76F9}" id="{BEA6A42C-CEC1-47E1-B002-6B6D239FF53A}">
     <text>39% GM non-gaap given Q422</text>
   </threadedComment>
-  <threadedComment ref="U103" dT="2026-01-17T19:03:25.79" personId="{885FAFCD-EA21-4344-9B78-0E93CEEF76F9}" id="{0577A713-2E0A-4E75-AF08-F9FA53908FBE}">
+  <threadedComment ref="U104" dT="2026-01-17T19:03:25.79" personId="{885FAFCD-EA21-4344-9B78-0E93CEEF76F9}" id="{0577A713-2E0A-4E75-AF08-F9FA53908FBE}">
     <text>Intel 7 node impairment</text>
   </threadedComment>
-  <threadedComment ref="Y103" dT="2026-01-17T19:08:50.09" personId="{885FAFCD-EA21-4344-9B78-0E93CEEF76F9}" id="{5269F9CD-AF19-4286-A693-FA2526B14A05}">
+  <threadedComment ref="Y104" dT="2026-01-17T19:08:50.09" personId="{885FAFCD-EA21-4344-9B78-0E93CEEF76F9}" id="{5269F9CD-AF19-4286-A693-FA2526B14A05}">
     <text>Add back writedown</text>
   </threadedComment>
 </ThreadedComments>
@@ -3194,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>48</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
@@ -3205,7 +3199,7 @@
         <v>1</v>
       </c>
       <c r="L3" s="2">
-        <v>4531</v>
+        <v>5026</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>147</v>
@@ -3220,7 +3214,7 @@
       </c>
       <c r="L4" s="2">
         <f>+L2*L3</f>
-        <v>217488</v>
+        <v>703640</v>
       </c>
       <c r="M4" s="3"/>
     </row>
@@ -3261,7 +3255,7 @@
       </c>
       <c r="L7" s="2">
         <f>+L4-L5+L6</f>
-        <v>224439</v>
+        <v>710591</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
@@ -3384,7 +3378,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B929D04B-6226-42F4-9686-EE1156E609DE}">
-  <dimension ref="A1:FW108"/>
+  <dimension ref="A1:FW109"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -6426,11 +6420,10 @@
         <v>13674</v>
       </c>
       <c r="AA30" s="7">
-        <f>+W30*0.95</f>
-        <v>12033.65</v>
+        <v>13577</v>
       </c>
       <c r="AB30" s="7">
-        <f t="shared" ref="AA30:AD30" si="38">+X30*0.9</f>
+        <f t="shared" ref="AB30:AD30" si="38">+X30*0.9</f>
         <v>11573.1</v>
       </c>
       <c r="AC30" s="7">
@@ -6725,7 +6718,9 @@
       <c r="Z31" s="5">
         <v>8731</v>
       </c>
-      <c r="AA31" s="5"/>
+      <c r="AA31" s="5">
+        <v>8230</v>
+      </c>
       <c r="AB31" s="5"/>
       <c r="AC31" s="5"/>
       <c r="AD31" s="5"/>
@@ -6950,7 +6945,10 @@
         <f>+Z30-Z31</f>
         <v>4943</v>
       </c>
-      <c r="AA32" s="5"/>
+      <c r="AA32" s="5">
+        <f>+AA30-AA31</f>
+        <v>5347</v>
+      </c>
       <c r="AB32" s="5"/>
       <c r="AC32" s="5"/>
       <c r="AD32" s="5"/>
@@ -7230,6 +7228,9 @@
       <c r="Z33" s="5">
         <v>3219</v>
       </c>
+      <c r="AA33" s="5">
+        <v>3375</v>
+      </c>
       <c r="BB33" s="36">
         <v>318.33100000000002</v>
       </c>
@@ -7452,6 +7453,9 @@
       <c r="Z34" s="5">
         <v>1174</v>
       </c>
+      <c r="AA34" s="5">
+        <v>1038</v>
+      </c>
       <c r="BB34" s="36">
         <v>456.2</v>
       </c>
@@ -7683,7 +7687,7 @@
         <v>4817</v>
       </c>
       <c r="X35" s="5">
-        <f t="shared" ref="X35:Z35" si="66">+X33+X34</f>
+        <f t="shared" ref="X35:AA35" si="66">+X33+X34</f>
         <v>4828</v>
       </c>
       <c r="Y35" s="5">
@@ -7694,7 +7698,10 @@
         <f t="shared" si="66"/>
         <v>4393</v>
       </c>
-      <c r="AA35" s="5"/>
+      <c r="AA35" s="5">
+        <f t="shared" si="66"/>
+        <v>4413</v>
+      </c>
       <c r="AB35" s="5"/>
       <c r="AC35" s="5"/>
       <c r="AD35" s="5"/>
@@ -7964,7 +7971,7 @@
         <v>-145</v>
       </c>
       <c r="X36" s="5">
-        <f t="shared" ref="X36:Z36" si="92">+X32-X35</f>
+        <f t="shared" ref="X36:AA36" si="92">+X32-X35</f>
         <v>-1286</v>
       </c>
       <c r="Y36" s="5">
@@ -7975,7 +7982,10 @@
         <f t="shared" si="92"/>
         <v>550</v>
       </c>
-      <c r="AA36" s="5"/>
+      <c r="AA36" s="5">
+        <f t="shared" si="92"/>
+        <v>934</v>
+      </c>
       <c r="AB36" s="5"/>
       <c r="AC36" s="5"/>
       <c r="AD36" s="5"/>
@@ -8233,6 +8243,9 @@
       <c r="Z37" s="3">
         <v>-145</v>
       </c>
+      <c r="AA37" s="3">
+        <v>-738</v>
+      </c>
       <c r="BB37" s="36">
         <v>110.955</v>
       </c>
@@ -8441,7 +8454,7 @@
         <v>-941</v>
       </c>
       <c r="U38" s="5">
-        <f t="shared" ref="U38:Z38" si="114">+U36+U37</f>
+        <f t="shared" ref="U38:AA38" si="114">+U36+U37</f>
         <v>-3305</v>
       </c>
       <c r="V38" s="5">
@@ -8464,7 +8477,10 @@
         <f t="shared" si="114"/>
         <v>405</v>
       </c>
-      <c r="AA38" s="5"/>
+      <c r="AA38" s="5">
+        <f t="shared" si="114"/>
+        <v>196</v>
+      </c>
       <c r="AB38" s="5"/>
       <c r="AC38" s="5"/>
       <c r="AD38" s="5"/>
@@ -8723,6 +8739,9 @@
       <c r="Z39" s="3">
         <v>671</v>
       </c>
+      <c r="AA39" s="3">
+        <v>0</v>
+      </c>
       <c r="BB39" s="36">
         <v>176.14</v>
       </c>
@@ -8942,7 +8961,7 @@
         <v>-941</v>
       </c>
       <c r="U40" s="5">
-        <f t="shared" ref="U40:Z40" si="136">+U38-U39</f>
+        <f t="shared" ref="U40:AA40" si="136">+U38-U39</f>
         <v>-3305</v>
       </c>
       <c r="V40" s="5">
@@ -8965,7 +8984,10 @@
         <f t="shared" si="136"/>
         <v>-266</v>
       </c>
-      <c r="AA40" s="5"/>
+      <c r="AA40" s="5">
+        <f t="shared" si="136"/>
+        <v>196</v>
+      </c>
       <c r="AB40" s="5"/>
       <c r="AC40" s="5"/>
       <c r="AD40" s="5"/>
@@ -9511,7 +9533,7 @@
         <v>-0.12581659811275103</v>
       </c>
       <c r="O41" s="16">
-        <f t="shared" ref="O41:Z41" si="171">+O40/O42</f>
+        <f t="shared" ref="O41:AA41" si="171">+O40/O42</f>
         <v>-0.3040442946557535</v>
       </c>
       <c r="P41" s="16">
@@ -9558,7 +9580,10 @@
         <f t="shared" si="171"/>
         <v>-5.4777594728171335E-2</v>
       </c>
-      <c r="AA41" s="16"/>
+      <c r="AA41" s="16">
+        <f t="shared" si="171"/>
+        <v>3.8559905567578205E-2</v>
+      </c>
       <c r="AB41" s="16"/>
       <c r="AC41" s="16"/>
       <c r="AD41" s="16"/>
@@ -9820,7 +9845,9 @@
       <c r="Z42" s="5">
         <v>4856</v>
       </c>
-      <c r="AA42" s="5"/>
+      <c r="AA42" s="5">
+        <v>5083</v>
+      </c>
       <c r="AB42" s="5"/>
       <c r="AC42" s="5"/>
       <c r="AD42" s="5"/>
@@ -10044,7 +10071,7 @@
         <v>-7.6933107315164895E-2</v>
       </c>
       <c r="R44" s="17">
-        <f t="shared" ref="R44:Z44" si="202">+R30/N30-1</f>
+        <f t="shared" ref="R44:AA44" si="202">+R30/N30-1</f>
         <v>9.7137159948725182E-2</v>
       </c>
       <c r="S44" s="17">
@@ -10079,7 +10106,10 @@
         <f t="shared" si="202"/>
         <v>-1.3804145570989634E-2</v>
       </c>
-      <c r="AA44" s="17"/>
+      <c r="AA44" s="17">
+        <f t="shared" si="202"/>
+        <v>7.1840214731191177E-2</v>
+      </c>
       <c r="AB44" s="17"/>
       <c r="AC44" s="17"/>
       <c r="AD44" s="17"/>
@@ -10611,7 +10641,7 @@
         <v>0.4</v>
       </c>
       <c r="W47" s="19">
-        <f t="shared" ref="W47:Z47" si="215">+W32/W30</f>
+        <f t="shared" ref="W47:AA47" si="215">+W32/W30</f>
         <v>0.36883239914739085</v>
       </c>
       <c r="X47" s="19">
@@ -10626,7 +10656,10 @@
         <f t="shared" si="215"/>
         <v>0.36148895714494661</v>
       </c>
-      <c r="AA47" s="19"/>
+      <c r="AA47" s="19">
+        <f t="shared" si="215"/>
+        <v>0.39382779700964865</v>
+      </c>
       <c r="AB47" s="19"/>
       <c r="AC47" s="19"/>
       <c r="AD47" s="19"/>
@@ -10759,7 +10792,7 @@
       </c>
       <c r="DA47" s="1">
         <f>+DA46/Main!L3</f>
-        <v>31.869379551941208</v>
+        <v>28.73063246117103</v>
       </c>
     </row>
     <row r="48" spans="2:179" x14ac:dyDescent="0.25">
@@ -10819,7 +10852,7 @@
       <c r="CW48" s="4"/>
       <c r="DA48" s="4">
         <f>+DA47/Main!L2-1</f>
-        <v>-0.33605459266789151</v>
+        <v>-0.79478119670592118</v>
       </c>
     </row>
     <row r="50" spans="2:105" x14ac:dyDescent="0.25">
@@ -10855,7 +10888,7 @@
         <v>-20654</v>
       </c>
       <c r="V50" s="5">
-        <f t="shared" ref="V50:Z50" si="223">+V51-V60</f>
+        <f t="shared" ref="V50:AA50" si="223">+V51-V60</f>
         <v>-22566</v>
       </c>
       <c r="W50" s="5">
@@ -10873,6 +10906,10 @@
       <c r="Z50" s="5">
         <f t="shared" si="223"/>
         <v>0</v>
+      </c>
+      <c r="AA50" s="5">
+        <f t="shared" si="223"/>
+        <v>-3761</v>
       </c>
       <c r="CJ50" s="2"/>
       <c r="CK50" s="2"/>
@@ -10969,6 +11006,10 @@
       <c r="Y51" s="5">
         <f>11141+19794+8667</f>
         <v>39602</v>
+      </c>
+      <c r="AA51" s="5">
+        <f>17247+15542+8481</f>
+        <v>41270</v>
       </c>
       <c r="CJ51" s="2"/>
       <c r="CK51" s="2"/>
@@ -11023,6 +11064,9 @@
       <c r="Y52" s="5">
         <v>3202</v>
       </c>
+      <c r="AA52" s="5">
+        <v>4066</v>
+      </c>
       <c r="CJ52" s="2"/>
       <c r="CK52" s="2"/>
       <c r="CL52" s="2"/>
@@ -11076,6 +11120,9 @@
       <c r="Y53" s="5">
         <v>11489</v>
       </c>
+      <c r="AA53" s="5">
+        <v>12426</v>
+      </c>
       <c r="CJ53" s="2"/>
       <c r="CK53" s="2"/>
       <c r="CL53" s="2"/>
@@ -11129,6 +11176,9 @@
       <c r="Y54" s="5">
         <v>6105</v>
       </c>
+      <c r="AA54" s="5">
+        <v>12876</v>
+      </c>
       <c r="CJ54" s="2"/>
       <c r="CK54" s="2"/>
       <c r="CL54" s="2"/>
@@ -11182,6 +11232,9 @@
       <c r="Y55" s="5">
         <v>105047</v>
       </c>
+      <c r="AA55" s="5">
+        <v>104458</v>
+      </c>
       <c r="CJ55" s="2"/>
       <c r="CK55" s="2"/>
       <c r="CL55" s="2"/>
@@ -11246,6 +11299,10 @@
         <f>23912+2877</f>
         <v>26789</v>
       </c>
+      <c r="AA56" s="5">
+        <f>20465+2722</f>
+        <v>23187</v>
+      </c>
       <c r="CJ56" s="2"/>
       <c r="CK56" s="2"/>
       <c r="CL56" s="2"/>
@@ -11299,6 +11356,9 @@
       <c r="Y57" s="5">
         <v>12280</v>
       </c>
+      <c r="AA57" s="5">
+        <v>7049</v>
+      </c>
       <c r="CJ57" s="2"/>
       <c r="CK57" s="2"/>
       <c r="CL57" s="2"/>
@@ -11348,7 +11408,7 @@
         <v>193542</v>
       </c>
       <c r="V58" s="5">
-        <f t="shared" ref="V58:Y58" si="226">SUM(V51:V57)</f>
+        <f t="shared" ref="V58:AA58" si="226">SUM(V51:V57)</f>
         <v>196485</v>
       </c>
       <c r="W58" s="5">
@@ -11362,6 +11422,14 @@
       <c r="Y58" s="5">
         <f t="shared" si="226"/>
         <v>204514</v>
+      </c>
+      <c r="Z58" s="5">
+        <f t="shared" si="226"/>
+        <v>0</v>
+      </c>
+      <c r="AA58" s="5">
+        <f t="shared" si="226"/>
+        <v>205332</v>
       </c>
       <c r="CJ58" s="2"/>
       <c r="CK58" s="2"/>
@@ -11444,6 +11512,10 @@
         <f>2496+44057</f>
         <v>46553</v>
       </c>
+      <c r="AA60" s="5">
+        <f>43027+2004</f>
+        <v>45031</v>
+      </c>
       <c r="CJ60" s="2"/>
       <c r="CK60" s="2"/>
       <c r="CL60" s="2"/>
@@ -11497,6 +11569,9 @@
       <c r="Y61" s="5">
         <v>10268</v>
       </c>
+      <c r="AA61" s="5">
+        <v>7159</v>
+      </c>
       <c r="CJ61" s="2"/>
       <c r="CK61" s="2"/>
       <c r="CL61" s="2"/>
@@ -11550,6 +11625,9 @@
       <c r="Y62" s="5">
         <v>3756</v>
       </c>
+      <c r="AA62" s="5">
+        <v>2824</v>
+      </c>
       <c r="CJ62" s="2"/>
       <c r="CK62" s="2"/>
       <c r="CL62" s="2"/>
@@ -11604,6 +11682,7 @@
       <c r="Y63" s="5">
         <v>825</v>
       </c>
+      <c r="AA63" s="5"/>
       <c r="CJ63" s="2"/>
       <c r="CK63" s="2"/>
       <c r="CL63" s="2"/>
@@ -11657,6 +11736,9 @@
       <c r="Y64" s="5">
         <v>14952</v>
       </c>
+      <c r="AA64" s="5">
+        <v>14898</v>
+      </c>
       <c r="CJ64" s="2"/>
       <c r="CK64" s="2"/>
       <c r="CL64" s="2"/>
@@ -11710,6 +11792,9 @@
       <c r="Y65" s="5">
         <v>11430</v>
       </c>
+      <c r="AA65" s="5">
+        <v>10431</v>
+      </c>
       <c r="CJ65" s="2"/>
       <c r="CK65" s="2"/>
       <c r="CL65" s="2"/>
@@ -11763,6 +11848,9 @@
       <c r="Y66" s="5">
         <v>116730</v>
       </c>
+      <c r="AA66" s="5">
+        <v>124989</v>
+      </c>
       <c r="CJ66" s="2"/>
       <c r="CK66" s="2"/>
       <c r="CL66" s="2"/>
@@ -11800,7 +11888,7 @@
         <v>191572</v>
       </c>
       <c r="S67" s="5">
-        <f t="shared" ref="S67:Y67" si="227">SUM(S60:S66)</f>
+        <f t="shared" ref="S67:AA67" si="227">SUM(S60:S66)</f>
         <v>192733</v>
       </c>
       <c r="T67" s="5">
@@ -11827,6 +11915,14 @@
         <f t="shared" si="227"/>
         <v>204514</v>
       </c>
+      <c r="Z67" s="5">
+        <f t="shared" si="227"/>
+        <v>0</v>
+      </c>
+      <c r="AA67" s="5">
+        <f t="shared" si="227"/>
+        <v>205332</v>
+      </c>
     </row>
     <row r="69" spans="2:105" x14ac:dyDescent="0.25">
       <c r="B69" s="2" t="s">
@@ -11849,7 +11945,7 @@
         <v>1432</v>
       </c>
       <c r="S69" s="5">
-        <f t="shared" ref="S69:Z69" si="229">+S40</f>
+        <f t="shared" ref="S69:AA69" si="229">+S40</f>
         <v>-576</v>
       </c>
       <c r="T69" s="5">
@@ -11880,6 +11976,10 @@
         <f t="shared" si="229"/>
         <v>-266</v>
       </c>
+      <c r="AA69" s="5">
+        <f t="shared" si="229"/>
+        <v>196</v>
+      </c>
       <c r="BS69" s="2">
         <f t="shared" ref="BS69:BZ69" si="230">+BS40</f>
         <v>7705</v>
@@ -11998,6 +12098,10 @@
         <f>359-X70-W70</f>
         <v>4270</v>
       </c>
+      <c r="Z70" s="5"/>
+      <c r="AA70" s="5">
+        <v>-4281</v>
+      </c>
       <c r="BS70" s="2">
         <v>8664</v>
       </c>
@@ -12097,6 +12201,10 @@
       <c r="Y71" s="5">
         <f>7971-X71-W71</f>
         <v>2758</v>
+      </c>
+      <c r="Z71" s="5"/>
+      <c r="AA71" s="5">
+        <v>2902</v>
       </c>
       <c r="BS71" s="2"/>
       <c r="BT71" s="28"/>
@@ -12156,6 +12264,10 @@
         <f>1896-X72-W72</f>
         <v>548</v>
       </c>
+      <c r="Z72" s="5"/>
+      <c r="AA72" s="5">
+        <v>621</v>
+      </c>
       <c r="BS72" s="2"/>
       <c r="BT72" s="28"/>
       <c r="BU72" s="2"/>
@@ -12214,6 +12326,10 @@
         <f>372-X73-W73</f>
         <v>-10</v>
       </c>
+      <c r="Z73" s="5"/>
+      <c r="AA73" s="5">
+        <v>3965</v>
+      </c>
       <c r="BS73" s="2"/>
       <c r="BT73" s="28"/>
       <c r="BU73" s="2"/>
@@ -12272,6 +12388,10 @@
         <f>708-X74-W74</f>
         <v>234</v>
       </c>
+      <c r="Z74" s="5"/>
+      <c r="AA74" s="5">
+        <v>234</v>
+      </c>
       <c r="BS74" s="2"/>
       <c r="BT74" s="28"/>
       <c r="BU74" s="2"/>
@@ -12330,6 +12450,11 @@
         <f>-611-X75-W75</f>
         <v>-221</v>
       </c>
+      <c r="Z75" s="5"/>
+      <c r="AA75" s="5">
+        <f>72+1090</f>
+        <v>1162</v>
+      </c>
       <c r="BS75" s="2"/>
       <c r="BT75" s="28"/>
       <c r="BU75" s="2"/>
@@ -12350,13 +12475,13 @@
       <c r="O76" s="5">
         <v>0</v>
       </c>
-      <c r="P76" s="3">
+      <c r="P76" s="5">
         <v>0</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="Q76" s="5">
         <v>0</v>
       </c>
-      <c r="R76" s="3">
+      <c r="R76" s="5">
         <v>0</v>
       </c>
       <c r="S76" s="5">
@@ -12383,6 +12508,10 @@
       <c r="Y76" s="5">
         <f>123-X76-W76</f>
         <v>17</v>
+      </c>
+      <c r="Z76" s="5"/>
+      <c r="AA76" s="5">
+        <v>-9</v>
       </c>
       <c r="BS76" s="2"/>
       <c r="BT76" s="28"/>
@@ -12398,13 +12527,13 @@
       <c r="O77" s="5">
         <v>0</v>
       </c>
-      <c r="P77" s="3">
+      <c r="P77" s="5">
         <v>0</v>
       </c>
-      <c r="Q77" s="3">
+      <c r="Q77" s="5">
         <v>0</v>
       </c>
-      <c r="R77" s="3">
+      <c r="R77" s="5">
         <v>0</v>
       </c>
       <c r="S77" s="5">
@@ -12431,6 +12560,10 @@
       <c r="Y77" s="5">
         <f>465-X77-W77</f>
         <v>-17</v>
+      </c>
+      <c r="Z77" s="5"/>
+      <c r="AA77" s="5">
+        <v>0</v>
       </c>
       <c r="BS77" s="2"/>
       <c r="BT77" s="28"/>
@@ -12446,36 +12579,40 @@
       <c r="O78" s="5">
         <v>0</v>
       </c>
-      <c r="P78" s="3">
+      <c r="P78" s="5">
         <v>0</v>
       </c>
-      <c r="Q78" s="3">
+      <c r="Q78" s="5">
         <v>0</v>
       </c>
-      <c r="R78" s="3">
+      <c r="R78" s="5">
         <v>0</v>
       </c>
       <c r="S78" s="5">
         <v>0</v>
       </c>
-      <c r="T78" s="3">
+      <c r="T78" s="5">
         <v>0</v>
       </c>
-      <c r="U78" s="3">
+      <c r="U78" s="5">
         <v>0</v>
       </c>
-      <c r="V78" s="3">
+      <c r="V78" s="5">
         <v>0</v>
       </c>
       <c r="W78" s="5">
         <v>0</v>
       </c>
-      <c r="X78" s="3">
+      <c r="X78" s="5">
         <v>0</v>
       </c>
       <c r="Y78" s="5">
         <f>1687-5355-X78-W78</f>
         <v>-3668</v>
+      </c>
+      <c r="Z78" s="5"/>
+      <c r="AA78" s="5">
+        <v>0</v>
       </c>
       <c r="BS78" s="2"/>
       <c r="BT78" s="28"/>
@@ -12537,6 +12674,11 @@
       <c r="Y79" s="5">
         <f>162-9-281+541-1196-1423-X79-W79</f>
         <v>-1365</v>
+      </c>
+      <c r="Z79" s="5"/>
+      <c r="AA79" s="5">
+        <f>-217-808-142-1175+169-1325</f>
+        <v>-3498</v>
       </c>
       <c r="BS79" s="2"/>
       <c r="BT79" s="28"/>
@@ -12587,7 +12729,7 @@
         <v>4054</v>
       </c>
       <c r="V80" s="5">
-        <f t="shared" ref="V80:Y80" si="234">SUM(V70:V79)</f>
+        <f t="shared" ref="V80:AA80" si="234">SUM(V70:V79)</f>
         <v>3165</v>
       </c>
       <c r="W80" s="5">
@@ -12605,6 +12747,10 @@
       <c r="Z80" s="5">
         <f>9697-Y80-X80-W80</f>
         <v>4288</v>
+      </c>
+      <c r="AA80" s="5">
+        <f t="shared" si="234"/>
+        <v>1096</v>
       </c>
       <c r="BS80" s="2">
         <v>14851</v>
@@ -12740,7 +12886,9 @@
         <f>-14646-Y82-X82-W82</f>
         <v>-3488</v>
       </c>
-      <c r="AA82" s="5"/>
+      <c r="AA82" s="5">
+        <v>-3636</v>
+      </c>
       <c r="AB82" s="5"/>
       <c r="AC82" s="5"/>
       <c r="AD82" s="5"/>
@@ -13280,7 +13428,7 @@
         <v>-3764</v>
       </c>
       <c r="W87" s="5">
-        <f t="shared" ref="W87:Y87" si="239">SUM(W82:W86)</f>
+        <f t="shared" ref="W87:AA87" si="239">SUM(W82:W86)</f>
         <v>81</v>
       </c>
       <c r="X87" s="5">
@@ -13291,8 +13439,14 @@
         <f t="shared" si="239"/>
         <v>-6250</v>
       </c>
-      <c r="Z87" s="5"/>
-      <c r="AA87" s="5"/>
+      <c r="Z87" s="5">
+        <f t="shared" si="239"/>
+        <v>-3488</v>
+      </c>
+      <c r="AA87" s="5">
+        <f t="shared" si="239"/>
+        <v>-3636</v>
+      </c>
       <c r="AB87" s="5"/>
       <c r="AC87" s="5"/>
       <c r="AD87" s="5"/>
@@ -13424,7 +13578,9 @@
         <v>-4247</v>
       </c>
       <c r="Z89" s="5"/>
-      <c r="AA89" s="5"/>
+      <c r="AA89" s="5">
+        <v>-1500</v>
+      </c>
       <c r="AB89" s="5"/>
       <c r="AC89" s="5"/>
       <c r="AD89" s="5"/>
@@ -13524,7 +13680,9 @@
         <v>1414</v>
       </c>
       <c r="Z90" s="5"/>
-      <c r="AA90" s="5"/>
+      <c r="AA90" s="5">
+        <v>2064</v>
+      </c>
       <c r="AB90" s="5"/>
       <c r="AC90" s="5"/>
       <c r="AD90" s="5"/>
@@ -13568,7 +13726,7 @@
     </row>
     <row r="91" spans="2:90" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B91" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C91" s="5"/>
       <c r="D91" s="5"/>
@@ -13582,36 +13740,21 @@
       <c r="L91" s="5"/>
       <c r="M91" s="5"/>
       <c r="N91" s="5"/>
-      <c r="O91" s="5">
-        <v>0</v>
-      </c>
-      <c r="P91" s="5">
-        <f>1573-O91</f>
-        <v>1573</v>
-      </c>
-      <c r="Q91" s="5">
-        <f>2423-P91-O91</f>
-        <v>850</v>
-      </c>
-      <c r="R91" s="5">
-        <f>2959-Q91-P91-O91</f>
-        <v>536</v>
-      </c>
-      <c r="S91" s="5">
-        <v>0</v>
-      </c>
-      <c r="T91" s="5">
-        <v>0</v>
-      </c>
-      <c r="U91" s="5">
-        <v>0</v>
-      </c>
+      <c r="O91" s="5"/>
+      <c r="P91" s="5"/>
+      <c r="Q91" s="5"/>
+      <c r="R91" s="5"/>
+      <c r="S91" s="5"/>
+      <c r="T91" s="5"/>
+      <c r="U91" s="5"/>
       <c r="V91" s="5"/>
       <c r="W91" s="5"/>
       <c r="X91" s="5"/>
       <c r="Y91" s="5"/>
       <c r="Z91" s="5"/>
-      <c r="AA91" s="5"/>
+      <c r="AA91" s="5">
+        <v>-1327</v>
+      </c>
       <c r="AB91" s="5"/>
       <c r="AC91" s="5"/>
       <c r="AD91" s="5"/>
@@ -13655,7 +13798,7 @@
     </row>
     <row r="92" spans="2:90" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B92" s="2" t="s">
-        <v>155</v>
+        <v>58</v>
       </c>
       <c r="C92" s="5"/>
       <c r="D92" s="5"/>
@@ -13670,45 +13813,33 @@
       <c r="M92" s="5"/>
       <c r="N92" s="5"/>
       <c r="O92" s="5">
-        <v>659</v>
+        <v>0</v>
       </c>
       <c r="P92" s="5">
-        <f>0-O92</f>
-        <v>-659</v>
+        <f>1573-O92</f>
+        <v>1573</v>
       </c>
       <c r="Q92" s="5">
+        <f>2423-P92-O92</f>
+        <v>850</v>
+      </c>
+      <c r="R92" s="5">
+        <f>2959-Q92-P92-O92</f>
+        <v>536</v>
+      </c>
+      <c r="S92" s="5">
         <v>0</v>
       </c>
-      <c r="R92" s="5">
-        <f>1042-Q92-P92-O92</f>
-        <v>1042</v>
-      </c>
-      <c r="S92" s="5">
-        <v>626</v>
-      </c>
       <c r="T92" s="5">
-        <f>631-S92</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U92" s="5">
-        <f>986-T92-S92</f>
-        <v>355</v>
-      </c>
-      <c r="V92" s="5">
-        <f>987-U92-T92-S92-631</f>
-        <v>-630</v>
-      </c>
-      <c r="W92" s="5">
-        <v>491</v>
-      </c>
-      <c r="X92" s="5">
-        <f>491-W92</f>
         <v>0</v>
       </c>
-      <c r="Y92" s="5">
-        <f>777-X92-W92</f>
-        <v>286</v>
-      </c>
+      <c r="V92" s="5"/>
+      <c r="W92" s="5"/>
+      <c r="X92" s="5"/>
+      <c r="Y92" s="5"/>
       <c r="Z92" s="5"/>
       <c r="AA92" s="5"/>
       <c r="AB92" s="5"/>
@@ -13754,7 +13885,7 @@
     </row>
     <row r="93" spans="2:90" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B93" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C93" s="5"/>
       <c r="D93" s="5"/>
@@ -13769,46 +13900,49 @@
       <c r="M93" s="5"/>
       <c r="N93" s="5"/>
       <c r="O93" s="5">
-        <v>-1512</v>
+        <v>659</v>
       </c>
       <c r="P93" s="5">
-        <f>-2036-O93</f>
-        <v>-524</v>
+        <f>0-O93</f>
+        <v>-659</v>
       </c>
       <c r="Q93" s="5">
-        <f>-2561-P93-O93</f>
-        <v>-525</v>
+        <v>0</v>
       </c>
       <c r="R93" s="5">
-        <f>-3088-Q93-P93-O93</f>
-        <v>-527</v>
+        <f>1042-Q93-P93-O93</f>
+        <v>1042</v>
       </c>
       <c r="S93" s="5">
-        <v>-529</v>
+        <v>626</v>
       </c>
       <c r="T93" s="5">
-        <f>-1063-S93</f>
-        <v>-534</v>
+        <f>631-S93</f>
+        <v>5</v>
       </c>
       <c r="U93" s="5">
-        <f>-1599-T93-S93</f>
-        <v>-536</v>
+        <f>986-T93-S93</f>
+        <v>355</v>
       </c>
       <c r="V93" s="5">
-        <f>-1599-U93-T93-S93</f>
+        <f>987-U93-T93-S93-631</f>
+        <v>-630</v>
+      </c>
+      <c r="W93" s="5">
+        <v>491</v>
+      </c>
+      <c r="X93" s="5">
+        <f>491-W93</f>
         <v>0</v>
       </c>
-      <c r="W93" s="5">
-        <v>0</v>
-      </c>
-      <c r="X93" s="5">
-        <v>0</v>
-      </c>
       <c r="Y93" s="5">
-        <v>0</v>
+        <f>777-X93-W93</f>
+        <v>286</v>
       </c>
       <c r="Z93" s="5"/>
-      <c r="AA93" s="5"/>
+      <c r="AA93" s="5">
+        <v>427</v>
+      </c>
       <c r="AB93" s="5"/>
       <c r="AC93" s="5"/>
       <c r="AD93" s="5"/>
@@ -13852,7 +13986,7 @@
     </row>
     <row r="94" spans="2:90" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B94" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C94" s="5"/>
       <c r="D94" s="5"/>
@@ -13867,46 +14001,43 @@
       <c r="M94" s="5"/>
       <c r="N94" s="5"/>
       <c r="O94" s="5">
-        <v>-225</v>
+        <v>-1512</v>
       </c>
       <c r="P94" s="5">
-        <f>212-O94</f>
-        <v>437</v>
+        <f>-2036-O94</f>
+        <v>-524</v>
       </c>
       <c r="Q94" s="5">
-        <f>457-P94-O94</f>
-        <v>245</v>
+        <f>-2561-P94-O94</f>
+        <v>-525</v>
       </c>
       <c r="R94" s="5">
-        <f>-847-Q94-P94-O94</f>
-        <v>-1304</v>
+        <f>-3088-Q94-P94-O94</f>
+        <v>-527</v>
       </c>
       <c r="S94" s="5">
-        <v>-220</v>
+        <v>-529</v>
       </c>
       <c r="T94" s="5">
-        <f>-444-S94</f>
-        <v>-224</v>
+        <f>-1063-S94</f>
+        <v>-534</v>
       </c>
       <c r="U94" s="5">
-        <f>-1277-T94-S94</f>
-        <v>-833</v>
+        <f>-1599-T94-S94</f>
+        <v>-536</v>
       </c>
       <c r="V94" s="5">
-        <f>-1178-U94-T94-S94+158</f>
-        <v>257</v>
+        <f>-1599-U94-T94-S94</f>
+        <v>0</v>
       </c>
       <c r="W94" s="5">
-        <f>-1020-618</f>
-        <v>-1638</v>
+        <v>0</v>
       </c>
       <c r="X94" s="5">
-        <f>-1962-W94-678</f>
-        <v>-1002</v>
+        <v>0</v>
       </c>
       <c r="Y94" s="5">
-        <f>922-X94-W94-2493+3737+3945-1052</f>
-        <v>7699</v>
+        <v>0</v>
       </c>
       <c r="Z94" s="5"/>
       <c r="AA94" s="5"/>
@@ -13953,7 +14084,7 @@
     </row>
     <row r="95" spans="2:90" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B95" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C95" s="5"/>
       <c r="D95" s="5"/>
@@ -13968,51 +14099,51 @@
       <c r="M95" s="5"/>
       <c r="N95" s="5"/>
       <c r="O95" s="5">
-        <f>SUM(O89:O94)</f>
-        <v>7394</v>
+        <v>-225</v>
       </c>
       <c r="P95" s="5">
-        <f>SUM(P89:P94)</f>
-        <v>117</v>
+        <f>212-O95</f>
+        <v>437</v>
       </c>
       <c r="Q95" s="5">
-        <f>SUM(Q89:Q94)</f>
-        <v>842</v>
+        <f>457-P95-O95</f>
+        <v>245</v>
       </c>
       <c r="R95" s="5">
-        <f t="shared" ref="R95:Y95" si="240">SUM(R89:R94)</f>
-        <v>152</v>
+        <f>-847-Q95-P95-O95</f>
+        <v>-1304</v>
       </c>
       <c r="S95" s="5">
-        <f t="shared" si="240"/>
-        <v>3630</v>
+        <v>-220</v>
       </c>
       <c r="T95" s="5">
-        <f t="shared" si="240"/>
-        <v>11237</v>
+        <f>-444-S95</f>
+        <v>-224</v>
       </c>
       <c r="U95" s="5">
-        <f t="shared" si="240"/>
-        <v>-3792</v>
+        <f>-1277-T95-S95</f>
+        <v>-833</v>
       </c>
       <c r="V95" s="5">
-        <f>SUM(V89:V94)</f>
-        <v>63</v>
+        <f>-1178-U95-T95-S95+158</f>
+        <v>257</v>
       </c>
       <c r="W95" s="5">
-        <f t="shared" si="240"/>
-        <v>-196</v>
+        <f>-1020-618</f>
+        <v>-1638</v>
       </c>
       <c r="X95" s="5">
-        <f t="shared" si="240"/>
-        <v>782</v>
+        <f>-1962-W95-678</f>
+        <v>-1002</v>
       </c>
       <c r="Y95" s="5">
-        <f t="shared" si="240"/>
-        <v>5152</v>
+        <f>922-X95-W95-2493+3737+3945-1052</f>
+        <v>7699</v>
       </c>
       <c r="Z95" s="5"/>
-      <c r="AA95" s="5"/>
+      <c r="AA95" s="5">
+        <v>-870</v>
+      </c>
       <c r="AB95" s="5"/>
       <c r="AC95" s="5"/>
       <c r="AD95" s="5"/>
@@ -14054,83 +14185,171 @@
       <c r="BV95" s="28"/>
       <c r="BW95" s="28"/>
     </row>
-    <row r="96" spans="2:90" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:90" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B96" s="2" t="s">
-        <v>158</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="C96" s="5"/>
+      <c r="D96" s="5"/>
+      <c r="E96" s="5"/>
+      <c r="F96" s="5"/>
+      <c r="G96" s="5"/>
+      <c r="H96" s="5"/>
+      <c r="I96" s="5"/>
+      <c r="J96" s="5"/>
+      <c r="K96" s="5"/>
+      <c r="L96" s="5"/>
+      <c r="M96" s="5"/>
+      <c r="N96" s="5"/>
       <c r="O96" s="5">
-        <f>+O95+O87+O80</f>
-        <v>-2912</v>
+        <f>SUM(O89:O95)</f>
+        <v>7394</v>
       </c>
       <c r="P96" s="5">
-        <f>+P95+P87+P80</f>
+        <f>SUM(P89:P95)</f>
         <v>117</v>
       </c>
       <c r="Q96" s="5">
-        <f>+Q95+Q87+Q80</f>
-        <v>-728</v>
+        <f>SUM(Q89:Q95)</f>
+        <v>842</v>
       </c>
       <c r="R96" s="5">
-        <f t="shared" ref="R96:Y96" si="241">+R95+R87+R80</f>
-        <v>-542</v>
+        <f t="shared" ref="R96:Y96" si="240">SUM(R89:R95)</f>
+        <v>152</v>
       </c>
       <c r="S96" s="5">
+        <f t="shared" si="240"/>
+        <v>3630</v>
+      </c>
+      <c r="T96" s="5">
+        <f t="shared" si="240"/>
+        <v>11237</v>
+      </c>
+      <c r="U96" s="5">
+        <f t="shared" si="240"/>
+        <v>-3792</v>
+      </c>
+      <c r="V96" s="5">
+        <f>SUM(V89:V95)</f>
+        <v>63</v>
+      </c>
+      <c r="W96" s="5">
+        <f t="shared" si="240"/>
+        <v>-196</v>
+      </c>
+      <c r="X96" s="5">
+        <f t="shared" si="240"/>
+        <v>782</v>
+      </c>
+      <c r="Y96" s="5">
+        <f t="shared" si="240"/>
+        <v>5152</v>
+      </c>
+      <c r="Z96" s="5">
+        <f t="shared" ref="Z96:AA96" si="241">SUM(Z89:Z95)</f>
+        <v>0</v>
+      </c>
+      <c r="AA96" s="5">
         <f t="shared" si="241"/>
-        <v>-156</v>
-      </c>
-      <c r="T96" s="5">
-        <f t="shared" si="241"/>
-        <v>4364</v>
-      </c>
-      <c r="U96" s="5">
-        <f t="shared" si="241"/>
-        <v>-2502</v>
-      </c>
-      <c r="V96" s="5">
-        <f t="shared" si="241"/>
-        <v>-536</v>
-      </c>
-      <c r="W96" s="5">
-        <f t="shared" si="241"/>
-        <v>698</v>
-      </c>
-      <c r="X96" s="5">
-        <f t="shared" si="241"/>
-        <v>746</v>
-      </c>
-      <c r="Y96" s="5">
-        <f t="shared" si="241"/>
-        <v>1448</v>
-      </c>
-      <c r="BS96" s="2"/>
+        <v>-1206</v>
+      </c>
+      <c r="AB96" s="5"/>
+      <c r="AC96" s="5"/>
+      <c r="AD96" s="5"/>
+      <c r="AI96" s="36"/>
+      <c r="AJ96" s="36"/>
+      <c r="AK96" s="36"/>
+      <c r="AL96" s="36"/>
+      <c r="AM96" s="36"/>
+      <c r="AN96" s="36"/>
+      <c r="AO96" s="28"/>
+      <c r="AP96" s="36"/>
+      <c r="AQ96" s="36"/>
+      <c r="AR96" s="36"/>
+      <c r="AS96" s="36"/>
+      <c r="AT96" s="36"/>
+      <c r="AU96" s="28"/>
+      <c r="AV96" s="36"/>
+      <c r="AW96" s="36"/>
+      <c r="AX96" s="36"/>
+      <c r="AY96" s="28"/>
+      <c r="AZ96" s="28"/>
+      <c r="BA96" s="36"/>
+      <c r="BB96" s="36"/>
+      <c r="BC96" s="28"/>
+      <c r="BD96" s="36"/>
+      <c r="BE96" s="36"/>
+      <c r="BF96" s="36"/>
+      <c r="BG96" s="36"/>
+      <c r="BH96" s="36"/>
+      <c r="BI96" s="36"/>
+      <c r="BJ96" s="36"/>
+      <c r="BK96" s="36"/>
+      <c r="BL96" s="28"/>
+      <c r="BM96" s="36"/>
+      <c r="BN96" s="36"/>
+      <c r="BO96" s="28"/>
+      <c r="BP96" s="28"/>
       <c r="BT96" s="28"/>
-      <c r="BU96" s="2"/>
       <c r="BV96" s="28"/>
       <c r="BW96" s="28"/>
-      <c r="BX96" s="2"/>
-      <c r="BY96" s="2"/>
-      <c r="BZ96" s="2"/>
-      <c r="CA96" s="2"/>
-      <c r="CB96" s="2"/>
-      <c r="CC96" s="2"/>
-      <c r="CD96" s="2"/>
-      <c r="CE96" s="2"/>
-      <c r="CF96" s="2"/>
-      <c r="CG96" s="2"/>
-      <c r="CH96" s="2"/>
-      <c r="CI96" s="2"/>
-      <c r="CJ96" s="2"/>
-      <c r="CK96" s="2"/>
-      <c r="CL96" s="2"/>
     </row>
     <row r="97" spans="2:90" x14ac:dyDescent="0.25">
-      <c r="B97" s="2"/>
-      <c r="S97" s="5"/>
-      <c r="T97" s="5"/>
-      <c r="U97" s="5"/>
-      <c r="V97" s="5"/>
-      <c r="W97" s="5"/>
-      <c r="X97" s="5"/>
+      <c r="B97" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="O97" s="5">
+        <f>+O96+O87+O80</f>
+        <v>-2912</v>
+      </c>
+      <c r="P97" s="5">
+        <f>+P96+P87+P80</f>
+        <v>117</v>
+      </c>
+      <c r="Q97" s="5">
+        <f>+Q96+Q87+Q80</f>
+        <v>-728</v>
+      </c>
+      <c r="R97" s="5">
+        <f t="shared" ref="R97:Y97" si="242">+R96+R87+R80</f>
+        <v>-542</v>
+      </c>
+      <c r="S97" s="5">
+        <f t="shared" si="242"/>
+        <v>-156</v>
+      </c>
+      <c r="T97" s="5">
+        <f t="shared" si="242"/>
+        <v>4364</v>
+      </c>
+      <c r="U97" s="5">
+        <f t="shared" si="242"/>
+        <v>-2502</v>
+      </c>
+      <c r="V97" s="5">
+        <f t="shared" si="242"/>
+        <v>-536</v>
+      </c>
+      <c r="W97" s="5">
+        <f t="shared" si="242"/>
+        <v>698</v>
+      </c>
+      <c r="X97" s="5">
+        <f t="shared" si="242"/>
+        <v>746</v>
+      </c>
+      <c r="Y97" s="5">
+        <f t="shared" si="242"/>
+        <v>1448</v>
+      </c>
+      <c r="Z97" s="5">
+        <f t="shared" ref="Z97:AA97" si="243">+Z96+Z87+Z80</f>
+        <v>800</v>
+      </c>
+      <c r="AA97" s="5">
+        <f t="shared" si="243"/>
+        <v>-3746</v>
+      </c>
       <c r="BS97" s="2"/>
       <c r="BT97" s="28"/>
       <c r="BU97" s="2"/>
@@ -14152,304 +14371,330 @@
       <c r="CK97" s="2"/>
       <c r="CL97" s="2"/>
     </row>
-    <row r="98" spans="2:90" ht="13" x14ac:dyDescent="0.3">
-      <c r="B98" s="2" t="s">
+    <row r="98" spans="2:90" x14ac:dyDescent="0.25">
+      <c r="B98" s="2"/>
+      <c r="S98" s="5"/>
+      <c r="T98" s="5"/>
+      <c r="U98" s="5"/>
+      <c r="V98" s="5"/>
+      <c r="W98" s="5"/>
+      <c r="X98" s="5"/>
+      <c r="BS98" s="2"/>
+      <c r="BT98" s="28"/>
+      <c r="BU98" s="2"/>
+      <c r="BV98" s="28"/>
+      <c r="BW98" s="28"/>
+      <c r="BX98" s="2"/>
+      <c r="BY98" s="2"/>
+      <c r="BZ98" s="2"/>
+      <c r="CA98" s="2"/>
+      <c r="CB98" s="2"/>
+      <c r="CC98" s="2"/>
+      <c r="CD98" s="2"/>
+      <c r="CE98" s="2"/>
+      <c r="CF98" s="2"/>
+      <c r="CG98" s="2"/>
+      <c r="CH98" s="2"/>
+      <c r="CI98" s="2"/>
+      <c r="CJ98" s="2"/>
+      <c r="CK98" s="2"/>
+      <c r="CL98" s="2"/>
+    </row>
+    <row r="99" spans="2:90" ht="13" x14ac:dyDescent="0.3">
+      <c r="B99" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="O98" s="5">
-        <f t="shared" ref="O98:U98" si="242">+O82+O80</f>
+      <c r="O99" s="5">
+        <f t="shared" ref="O99:U99" si="244">+O82+O80</f>
         <v>-9198</v>
       </c>
-      <c r="P98" s="5">
-        <f t="shared" si="242"/>
+      <c r="P99" s="5">
+        <f t="shared" si="244"/>
         <v>-3080</v>
       </c>
-      <c r="Q98" s="5">
-        <f t="shared" si="242"/>
+      <c r="Q99" s="5">
+        <f t="shared" si="244"/>
         <v>71</v>
       </c>
-      <c r="R98" s="5">
-        <f t="shared" si="242"/>
+      <c r="R99" s="5">
+        <f t="shared" si="244"/>
         <v>-2072</v>
       </c>
-      <c r="S98" s="5">
-        <f t="shared" si="242"/>
+      <c r="S99" s="5">
+        <f t="shared" si="244"/>
         <v>-7193</v>
       </c>
-      <c r="T98" s="5">
-        <f t="shared" si="242"/>
+      <c r="T99" s="5">
+        <f t="shared" si="244"/>
         <v>-3390</v>
       </c>
-      <c r="U98" s="5">
-        <f t="shared" si="242"/>
+      <c r="U99" s="5">
+        <f t="shared" si="244"/>
         <v>-2404</v>
       </c>
-      <c r="V98" s="5">
-        <f t="shared" ref="V98:Z98" si="243">+V82+V80</f>
+      <c r="V99" s="5">
+        <f t="shared" ref="V99:AA99" si="245">+V82+V80</f>
         <v>-2669</v>
       </c>
-      <c r="W98" s="5">
-        <f t="shared" si="243"/>
+      <c r="W99" s="5">
+        <f t="shared" si="245"/>
         <v>-4370</v>
       </c>
-      <c r="X98" s="5">
-        <f t="shared" si="243"/>
+      <c r="X99" s="5">
+        <f t="shared" si="245"/>
         <v>-1500</v>
       </c>
-      <c r="Y98" s="5">
-        <f t="shared" si="243"/>
+      <c r="Y99" s="5">
+        <f t="shared" si="245"/>
         <v>121</v>
       </c>
-      <c r="Z98" s="5">
-        <f t="shared" si="243"/>
+      <c r="Z99" s="5">
+        <f t="shared" si="245"/>
         <v>800</v>
       </c>
-      <c r="BS98" s="6">
-        <f t="shared" ref="BS98:CE98" si="244">+BS80-BS82</f>
+      <c r="AA99" s="5">
+        <f t="shared" si="245"/>
+        <v>-2540</v>
+      </c>
+      <c r="BS99" s="6">
+        <f t="shared" ref="BS99:CE99" si="246">+BS80-BS82</f>
         <v>8980</v>
       </c>
-      <c r="BT98" s="29">
-        <f t="shared" si="244"/>
+      <c r="BT99" s="29">
+        <f t="shared" si="246"/>
         <v>4772</v>
       </c>
-      <c r="BU98" s="6">
-        <f t="shared" si="244"/>
+      <c r="BU99" s="6">
+        <f t="shared" si="246"/>
         <v>7625</v>
       </c>
-      <c r="BV98" s="29">
-        <f t="shared" si="244"/>
+      <c r="BV99" s="29">
+        <f t="shared" si="246"/>
         <v>5729</v>
       </c>
-      <c r="BW98" s="29">
-        <f t="shared" si="244"/>
+      <c r="BW99" s="29">
+        <f t="shared" si="246"/>
         <v>6655</v>
       </c>
-      <c r="BX98" s="6">
-        <f t="shared" si="244"/>
+      <c r="BX99" s="6">
+        <f t="shared" si="246"/>
         <v>11485</v>
       </c>
-      <c r="BY98" s="6">
-        <f t="shared" si="244"/>
+      <c r="BY99" s="6">
+        <f t="shared" si="246"/>
         <v>15756</v>
       </c>
-      <c r="BZ98" s="6">
-        <f t="shared" si="244"/>
+      <c r="BZ99" s="6">
+        <f t="shared" si="246"/>
         <v>7857</v>
       </c>
-      <c r="CA98" s="6">
-        <f t="shared" si="244"/>
+      <c r="CA99" s="6">
+        <f t="shared" si="246"/>
         <v>10065</v>
       </c>
-      <c r="CB98" s="6">
-        <f t="shared" si="244"/>
+      <c r="CB99" s="6">
+        <f t="shared" si="246"/>
         <v>10313</v>
       </c>
-      <c r="CC98" s="6">
-        <f t="shared" si="244"/>
+      <c r="CC99" s="6">
+        <f t="shared" si="246"/>
         <v>11691</v>
       </c>
-      <c r="CD98" s="6">
-        <f t="shared" si="244"/>
+      <c r="CD99" s="6">
+        <f t="shared" si="246"/>
         <v>12183</v>
       </c>
-      <c r="CE98" s="6">
-        <f t="shared" si="244"/>
+      <c r="CE99" s="6">
+        <f t="shared" si="246"/>
         <v>10332</v>
       </c>
-      <c r="CF98" s="6">
-        <f t="shared" ref="CF98:CL98" si="245">+CF80+CF82</f>
+      <c r="CF99" s="6">
+        <f t="shared" ref="CF99:CL99" si="247">+CF80+CF82</f>
         <v>14251</v>
       </c>
-      <c r="CG98" s="6">
-        <f t="shared" si="245"/>
+      <c r="CG99" s="6">
+        <f t="shared" si="247"/>
         <v>16932</v>
       </c>
-      <c r="CH98" s="6">
-        <f t="shared" si="245"/>
+      <c r="CH99" s="6">
+        <f t="shared" si="247"/>
         <v>21605</v>
       </c>
-      <c r="CI98" s="6">
-        <f t="shared" si="245"/>
+      <c r="CI99" s="6">
+        <f t="shared" si="247"/>
         <v>10723</v>
       </c>
-      <c r="CJ98" s="6">
-        <f t="shared" si="245"/>
+      <c r="CJ99" s="6">
+        <f t="shared" si="247"/>
         <v>-9411</v>
       </c>
-      <c r="CK98" s="6">
-        <f t="shared" si="245"/>
+      <c r="CK99" s="6">
+        <f t="shared" si="247"/>
         <v>-14279</v>
       </c>
-      <c r="CL98" s="6">
-        <f t="shared" si="245"/>
+      <c r="CL99" s="6">
+        <f t="shared" si="247"/>
         <v>-15656</v>
       </c>
     </row>
-    <row r="99" spans="2:90" x14ac:dyDescent="0.25">
-      <c r="B99" s="2" t="s">
+    <row r="100" spans="2:90" x14ac:dyDescent="0.25">
+      <c r="B100" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="BY99" s="2">
-        <f t="shared" ref="BY99:CL99" si="246">+BY40-BY98</f>
+      <c r="BY100" s="2">
+        <f t="shared" ref="BY100:CL100" si="248">+BY40-BY99</f>
         <v>-3050</v>
       </c>
-      <c r="BZ99" s="2">
-        <f t="shared" si="246"/>
+      <c r="BZ100" s="2">
+        <f t="shared" si="248"/>
         <v>3127</v>
       </c>
-      <c r="CA99" s="2">
-        <f t="shared" si="246"/>
+      <c r="CA100" s="2">
+        <f t="shared" si="248"/>
         <v>-385</v>
       </c>
-      <c r="CB99" s="2">
-        <f t="shared" si="246"/>
+      <c r="CB100" s="2">
+        <f t="shared" si="248"/>
         <v>1569</v>
       </c>
-      <c r="CC99" s="2">
-        <f t="shared" si="246"/>
+      <c r="CC100" s="2">
+        <f t="shared" si="248"/>
         <v>33</v>
       </c>
-      <c r="CD99" s="2">
-        <f t="shared" si="246"/>
+      <c r="CD100" s="2">
+        <f t="shared" si="248"/>
         <v>-193</v>
       </c>
-      <c r="CE99" s="2">
-        <f t="shared" si="246"/>
+      <c r="CE100" s="2">
+        <f t="shared" si="248"/>
         <v>7930</v>
       </c>
-      <c r="CF99" s="2">
-        <f t="shared" si="246"/>
+      <c r="CF100" s="2">
+        <f t="shared" si="248"/>
         <v>6855</v>
       </c>
-      <c r="CG99" s="2">
-        <f t="shared" si="246"/>
+      <c r="CG100" s="2">
+        <f t="shared" si="248"/>
         <v>2970</v>
       </c>
-      <c r="CH99" s="2">
-        <f t="shared" si="246"/>
+      <c r="CH100" s="2">
+        <f t="shared" si="248"/>
         <v>-2412</v>
       </c>
-      <c r="CI99" s="2">
-        <f t="shared" si="246"/>
+      <c r="CI100" s="2">
+        <f t="shared" si="248"/>
         <v>9042</v>
       </c>
-      <c r="CJ99" s="2">
-        <f t="shared" si="246"/>
+      <c r="CJ100" s="2">
+        <f t="shared" si="248"/>
         <v>13162</v>
       </c>
-      <c r="CK99" s="2">
-        <f t="shared" si="246"/>
+      <c r="CK100" s="2">
+        <f t="shared" si="248"/>
         <v>14811</v>
       </c>
-      <c r="CL99" s="2">
-        <f t="shared" si="246"/>
+      <c r="CL100" s="2">
+        <f t="shared" si="248"/>
         <v>11630.16</v>
       </c>
     </row>
-    <row r="101" spans="2:90" x14ac:dyDescent="0.25">
-      <c r="B101" t="s">
+    <row r="102" spans="2:90" x14ac:dyDescent="0.25">
+      <c r="B102" t="s">
         <v>82</v>
       </c>
-      <c r="P101" s="5">
+      <c r="P102" s="5">
         <v>126800</v>
       </c>
-      <c r="Q101" s="5"/>
-      <c r="R101" s="5"/>
-      <c r="S101" s="5">
+      <c r="Q102" s="5"/>
+      <c r="R102" s="5"/>
+      <c r="S102" s="5">
         <v>125200</v>
       </c>
-      <c r="T101" s="5">
+      <c r="T102" s="5">
         <v>125300</v>
       </c>
     </row>
-    <row r="103" spans="2:90" x14ac:dyDescent="0.25">
-      <c r="B103" t="s">
+    <row r="104" spans="2:90" x14ac:dyDescent="0.25">
+      <c r="B104" t="s">
         <v>287</v>
       </c>
-      <c r="N103" s="5">
-        <f>-5169-M103-L103-K103</f>
+      <c r="N104" s="5">
+        <f>-5169-M104-L104-K104</f>
         <v>-5169</v>
       </c>
-      <c r="Q103" s="5">
+      <c r="Q104" s="5">
         <v>-1407</v>
       </c>
-      <c r="R103" s="5">
-        <f>-6955-Q103-P103-O103</f>
+      <c r="R104" s="5">
+        <f>-6955-Q104-P104-O104</f>
         <v>-5548</v>
       </c>
-      <c r="S103" s="5">
+      <c r="S104" s="5">
         <v>-2441</v>
       </c>
-      <c r="T103" s="5">
+      <c r="T104" s="5">
         <v>-2802</v>
       </c>
-      <c r="U103" s="5">
+      <c r="U104" s="5">
         <f>-5844+2100+945</f>
         <v>-2799</v>
       </c>
-      <c r="V103" s="5">
-        <f>-13408-U103-T103-S103</f>
+      <c r="V104" s="5">
+        <f>-13408-U104-T104-S104</f>
         <v>-5366</v>
       </c>
-      <c r="W103" s="5">
+      <c r="W104" s="5">
         <v>-2320</v>
       </c>
-      <c r="X103" s="5">
+      <c r="X104" s="5">
         <f>-3168+460+337</f>
         <v>-2371</v>
       </c>
-      <c r="Y103" s="5">
+      <c r="Y104" s="5">
         <f>-2321+460+337</f>
         <v>-1524</v>
       </c>
     </row>
-    <row r="104" spans="2:90" x14ac:dyDescent="0.25">
-      <c r="B104" t="s">
+    <row r="105" spans="2:90" x14ac:dyDescent="0.25">
+      <c r="B105" t="s">
         <v>289</v>
       </c>
-      <c r="Q104" s="5">
-        <f t="shared" ref="Q104:X104" si="247">+Q103+Q80</f>
+      <c r="Q105" s="5">
+        <f t="shared" ref="Q105:X105" si="249">+Q104+Q80</f>
         <v>4417</v>
       </c>
-      <c r="R104" s="5">
-        <f t="shared" si="247"/>
+      <c r="R105" s="5">
+        <f t="shared" si="249"/>
         <v>-924</v>
       </c>
-      <c r="S104" s="5">
-        <f t="shared" si="247"/>
+      <c r="S105" s="5">
+        <f t="shared" si="249"/>
         <v>-3664</v>
       </c>
-      <c r="T104" s="5">
-        <f t="shared" si="247"/>
+      <c r="T105" s="5">
+        <f t="shared" si="249"/>
         <v>-510</v>
       </c>
-      <c r="U104" s="5">
-        <f t="shared" si="247"/>
+      <c r="U105" s="5">
+        <f t="shared" si="249"/>
         <v>1255</v>
       </c>
-      <c r="V104" s="5">
-        <f t="shared" si="247"/>
+      <c r="V105" s="5">
+        <f t="shared" si="249"/>
         <v>-2201</v>
       </c>
-      <c r="W104" s="5">
-        <f t="shared" si="247"/>
+      <c r="W105" s="5">
+        <f t="shared" si="249"/>
         <v>-1507</v>
       </c>
-      <c r="X104" s="5">
-        <f t="shared" si="247"/>
+      <c r="X105" s="5">
+        <f t="shared" si="249"/>
         <v>-321</v>
       </c>
-      <c r="Y104" s="5">
-        <f>+Y103+Y80</f>
+      <c r="Y105" s="5">
+        <f>+Y104+Y80</f>
         <v>1022</v>
       </c>
-    </row>
-    <row r="105" spans="2:90" x14ac:dyDescent="0.25">
-      <c r="Q105" s="5"/>
-      <c r="R105" s="5"/>
-      <c r="S105" s="5"/>
-      <c r="T105" s="5"/>
-      <c r="U105" s="5"/>
     </row>
     <row r="106" spans="2:90" x14ac:dyDescent="0.25">
       <c r="Q106" s="5"/>
@@ -14458,11 +14703,18 @@
       <c r="T106" s="5"/>
       <c r="U106" s="5"/>
     </row>
-    <row r="108" spans="2:90" x14ac:dyDescent="0.25">
-      <c r="B108" t="s">
+    <row r="107" spans="2:90" x14ac:dyDescent="0.25">
+      <c r="Q107" s="5"/>
+      <c r="R107" s="5"/>
+      <c r="S107" s="5"/>
+      <c r="T107" s="5"/>
+      <c r="U107" s="5"/>
+    </row>
+    <row r="109" spans="2:90" x14ac:dyDescent="0.25">
+      <c r="B109" t="s">
         <v>257</v>
       </c>
-      <c r="U108" s="5">
+      <c r="U109" s="5">
         <f>+U66-U56</f>
         <v>76209</v>
       </c>
